--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0009.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0009.xlsx
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>SPD TẤN CÔNG</t>
+          <t>SPD ATK</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Ranking</t>
+          <t>Xếp hạng</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Trở về</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Ranking</t>
+          <t>Xếp hạng</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=Touch} bất cứ đâu để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Tap} bất cứ đâu để đóng</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Nhấp Tay cầm=Nhấn} để nhận</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Tap} để nhận</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Mới</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Endstate Matrix</t>
+          <t>Ma Trận Endstate</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Endstate Matrix</t>
+          <t>Ma Trận Endstate</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Lineup</t>
+          <t>Đội hình</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Endstate Matrix</t>
+          <t>Ma Trận Endstate</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Lineup</t>
+          <t>Đội hình</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Endstate Matrix</t>
+          <t>Ma Trận Endstate</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Endstate Matrix</t>
+          <t>Ma Trận Endstate</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Trở về</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Trở về</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Increase GPA Level</t>
+          <t>Tăng Cấp Độ GPA</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Bộ lọc</t>
         </is>
       </c>
     </row>
